--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484077_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484077_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6697</v>
+        <v>5.6006</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6678</v>
+        <v>7.4023</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9981</v>
+        <v>-1.8017</v>
       </c>
       <c r="G2" t="n">
         <v>-1.4032</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5606</v>
+        <v>1.3703</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7368</v>
+        <v>0.9977</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1762</v>
+        <v>0.3726</v>
       </c>
       <c r="V2" t="n">
         <v>4.6416</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9407</v>
+        <v>2.5249</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6634</v>
+        <v>7.0513</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.7228</v>
+        <v>-4.5264</v>
       </c>
       <c r="G3" t="n">
         <v>4.743</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0322</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1678</v>
+        <v>0.5556</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1356</v>
+        <v>0.0608</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2555</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6073</v>
+        <v>0.3858</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4596</v>
+        <v>1.1335</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.7477</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9282</v>
+        <v>-1.9756</v>
       </c>
       <c r="H4" t="n">
-        <v>0.348</v>
+        <v>-1.1594</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2762</v>
+        <v>-0.8162</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1801</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6167</v>
+        <v>0.3077</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4367</v>
+        <v>0.4921</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.1082</v>
+        <v>-2.7755</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2687</v>
+        <v>-1.4671</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8395</v>
+        <v>-1.3084</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.7693</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.9515</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>5.5485</v>
+        <v>1.1407</v>
       </c>
       <c r="T4" t="n">
-        <v>4.0246</v>
+        <v>1.111</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5239</v>
+        <v>0.0297</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7562</v>
+        <v>1.2207</v>
       </c>
       <c r="W4" t="n">
         <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4503</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.426</v>
+        <v>0.2455</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1105</v>
+        <v>2.131</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6845</v>
+        <v>-1.8855</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5583</v>
+        <v>-1.5702</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0187</v>
+        <v>-1.2398</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.5769</v>
+        <v>-0.3303</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0286</v>
+        <v>0.7658</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5482</v>
+        <v>-0.6399</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5195</v>
+        <v>1.4057</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5869</v>
+        <v>-2.336</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5295</v>
+        <v>-0.6</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.0574</v>
+        <v>-1.736</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S5" t="n">
-        <v>4.0952</v>
+        <v>0.2721</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8512</v>
+        <v>0.1587</v>
       </c>
       <c r="U5" t="n">
-        <v>1.244</v>
+        <v>0.1133</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6745</v>
+        <v>1.3452</v>
       </c>
       <c r="W5" t="n">
         <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.532</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MESA RUIZ</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0168</v>
+        <v>-0.0389</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7457</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7289</v>
+        <v>-0.9799</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.949</v>
+        <v>0.4657</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3983</v>
+        <v>-0.3933</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3474</v>
+        <v>0.8589</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2525</v>
+        <v>1.0657</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9327</v>
+        <v>0.3427</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6802</v>
+        <v>0.7229</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2016</v>
+        <v>-0.6</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5344</v>
+        <v>-0.736</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6672</v>
+        <v>0.136</v>
       </c>
       <c r="P6" t="n">
         <v>0.1984</v>
@@ -922,28 +922,28 @@
         <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7675</v>
+        <v>-0.1672</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4932</v>
+        <v>-0.1247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2743</v>
+        <v>-0.0425</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5358000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>A. MESA RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.095</v>
+        <v>-0.1413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.6437</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.036</v>
+        <v>-0.785</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4657</v>
+        <v>-0.949</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3933</v>
+        <v>0.3983</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8589</v>
+        <v>-1.3474</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0657</v>
+        <v>0.2525</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3427</v>
+        <v>0.9327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7229</v>
+        <v>-0.6802</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6</v>
+        <v>-1.2016</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.736</v>
+        <v>-0.5344</v>
       </c>
       <c r="O7" t="n">
-        <v>0.136</v>
+        <v>-0.6672</v>
       </c>
       <c r="P7" t="n">
         <v>0.1984</v>
@@ -1000,28 +1000,28 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2233</v>
+        <v>0.6093</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1247</v>
+        <v>0.3911</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.2182</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5358000000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5358000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2749</v>
+        <v>-0.3565</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7229</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9977</v>
+        <v>-0.3565</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5702</v>
+        <v>-0.4032</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2398</v>
+        <v>-0.4032</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3303</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7658</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6399</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4057</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.336</v>
+        <v>-0.4032</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6</v>
+        <v>-0.4032</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.736</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2483</v>
+        <v>0.0468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2494</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0011</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3452</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>S. BACHIOCHI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3845</v>
+        <v>-0.8312</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.0161</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3845</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4032</v>
+        <v>-0.9247</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4032</v>
+        <v>-0.6099</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.3148</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.1408</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0803</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4032</v>
+        <v>-1.0655</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4032</v>
+        <v>-0.6704</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.3951</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0187</v>
+        <v>-0.3033</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.1247</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>-0.1786</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5605</v>
+        <v>-1.2191</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2153</v>
+        <v>0.8862</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7758</v>
+        <v>-2.1053</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9756</v>
+        <v>-2.5583</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1594</v>
+        <v>1.0187</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8162</v>
+        <v>-3.5769</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7999000000000001</v>
+        <v>1.0286</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3077</v>
+        <v>1.5482</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4921</v>
+        <v>-0.5195</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7755</v>
+        <v>-3.5869</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4671</v>
+        <v>-0.5295</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3084</v>
+        <v>-3.0574</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9838</v>
+        <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1944</v>
+        <v>2.4501</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1928</v>
+        <v>1.6269</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0016</v>
+        <v>0.8232</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2207</v>
+        <v>0.6745</v>
       </c>
       <c r="W10" t="n">
         <v>1.2065</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0143</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. BACHIOCHI</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8873</v>
+        <v>-1.8893</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0161</v>
+        <v>0.0508</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9034</v>
+        <v>-1.9401</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9247</v>
+        <v>-3.971</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6099</v>
+        <v>-0.6101</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3148</v>
+        <v>-3.3608</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1408</v>
+        <v>-0.1023</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0605</v>
+        <v>0.7258</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0803</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0655</v>
+        <v>-3.8687</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6704</v>
+        <v>-1.336</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3951</v>
+        <v>-2.5327</v>
       </c>
       <c r="P11" t="n">
         <v>0.3968</v>
@@ -1312,28 +1312,28 @@
         <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3594</v>
+        <v>0.3217</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1247</v>
+        <v>0.1531</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2347</v>
+        <v>0.1686</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.3633</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.3633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9121</v>
+        <v>-2.3949</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6634</v>
+        <v>-0.7851</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2487</v>
+        <v>-1.6098</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.971</v>
+        <v>-1.9282</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6101</v>
+        <v>0.348</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3608</v>
+        <v>-2.2762</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1023</v>
+        <v>2.1801</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7258</v>
+        <v>2.6167</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.4367</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.8687</v>
+        <v>-4.1082</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.336</v>
+        <v>-2.2687</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.5327</v>
+        <v>-1.8395</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3968</v>
+        <v>-3.7693</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-5.9515</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7010999999999999</v>
+        <v>2.5464</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5611</v>
+        <v>1.7799</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.14</v>
+        <v>0.7665</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3633</v>
+        <v>0.7562</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X12" t="n">
-        <v>1.3633</v>
+        <v>-0.4503</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3957</v>
+        <v>-2.7351</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2228</v>
+        <v>-0.8147</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1728</v>
+        <v>-1.9203</v>
       </c>
       <c r="G13" t="n">
         <v>-1.983</v>
@@ -1468,13 +1468,13 @@
         <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0436</v>
+        <v>0.7043</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0113</v>
+        <v>0.4195</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0323</v>
+        <v>0.2848</v>
       </c>
       <c r="V13" t="n">
         <v>-0.266</v>
@@ -1513,7 +1513,7 @@
         <v>-12.4577</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3035000000000001</v>
+        <v>0.3034999999999998</v>
       </c>
       <c r="I14" t="n">
         <v>-12.7611</v>
@@ -1546,13 +1546,13 @@
         <v>10.9111</v>
       </c>
       <c r="S14" t="n">
-        <v>9.607399999999998</v>
+        <v>9.6076</v>
       </c>
       <c r="T14" t="n">
-        <v>6.944200000000001</v>
+        <v>6.944100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6632</v>
+        <v>2.663400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>8.9442</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8358</v>
+        <v>4.1811</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3959</v>
+        <v>4.8858</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5602</v>
+        <v>-0.7047</v>
       </c>
       <c r="G15" t="n">
         <v>3.6362</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0113</v>
+        <v>-0.666</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4252</v>
+        <v>-0.0849</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4366</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>2.0044</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.751</v>
+        <v>3.7071</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0068</v>
+        <v>5.4507</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2558</v>
+        <v>-1.7436</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7069</v>
+        <v>4.7727</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3886</v>
+        <v>1.2345</v>
       </c>
       <c r="I16" t="n">
-        <v>6.0955</v>
+        <v>3.5382</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4744</v>
+        <v>6.1515</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8065</v>
+        <v>1.6936</v>
       </c>
       <c r="L16" t="n">
-        <v>5.6679</v>
+        <v>4.4579</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7674</v>
+        <v>-1.3788</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.195</v>
+        <v>-0.459</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4276</v>
+        <v>-0.9198</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5944</v>
+        <v>-0.9267</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1303</v>
+        <v>-0.3797</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4641</v>
+        <v>-0.547</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1469</v>
+        <v>-0.3373</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3373</v>
+        <v>0.8692</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8097</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3449</v>
+        <v>3.6974</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1446</v>
+        <v>5.7007</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7997</v>
+        <v>-2.0033</v>
       </c>
       <c r="G17" t="n">
-        <v>4.7727</v>
+        <v>5.7069</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2345</v>
+        <v>-0.3886</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5382</v>
+        <v>6.0955</v>
       </c>
       <c r="J17" t="n">
-        <v>6.1515</v>
+        <v>6.4744</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6936</v>
+        <v>0.8065</v>
       </c>
       <c r="L17" t="n">
-        <v>4.4579</v>
+        <v>5.6679</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3788</v>
+        <v>-0.7674</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.459</v>
+        <v>-1.195</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9198</v>
+        <v>0.4276</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2889</v>
+        <v>-1.648</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6858</v>
+        <v>-0.4364</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6031</v>
+        <v>-1.2116</v>
       </c>
       <c r="V17" t="n">
+        <v>-2.1469</v>
+      </c>
+      <c r="W17" t="n">
         <v>-0.3373</v>
       </c>
-      <c r="W17" t="n">
-        <v>0.8692</v>
-      </c>
       <c r="X17" t="n">
-        <v>-1.2065</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5222</v>
+        <v>-0.1032</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4478</v>
+        <v>3.4652</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9257</v>
+        <v>-3.5684</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.163</v>
+        <v>2.8047</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4415</v>
+        <v>1.114</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7215</v>
+        <v>1.6907</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0174</v>
+        <v>5.849</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6961000000000001</v>
+        <v>3.1155</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3213</v>
+        <v>2.7335</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1803</v>
+        <v>-3.0443</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1375</v>
+        <v>-2.0015</v>
       </c>
       <c r="O18" t="n">
         <v>-1.0428</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R18" t="n">
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4353</v>
+        <v>-0.7411</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3629</v>
+        <v>-0.4477</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.2934</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>-3.1587</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>-0.7458</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0696</v>
+        <v>-0.1427</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2177</v>
+        <v>1.0397</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2873</v>
+        <v>-1.1824</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2838</v>
+        <v>-2.163</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4484</v>
+        <v>-1.4415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1646</v>
+        <v>-0.7215</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2917</v>
+        <v>1.0174</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0106</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2811</v>
+        <v>0.3213</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5756</v>
+        <v>-3.1803</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.459</v>
+        <v>-2.1375</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1165</v>
+        <v>-1.0428</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.2296</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0567</v>
+        <v>-0.0452</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8939</v>
+        <v>-0.1843</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8692</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7672</v>
+        <v>-0.3476</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8531</v>
+        <v>0.9116</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6203</v>
+        <v>-1.2592</v>
       </c>
       <c r="G20" t="n">
-        <v>2.8047</v>
+        <v>-0.2838</v>
       </c>
       <c r="H20" t="n">
-        <v>1.114</v>
+        <v>-0.4484</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6907</v>
+        <v>0.1646</v>
       </c>
       <c r="J20" t="n">
-        <v>5.849</v>
+        <v>0.2917</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1155</v>
+        <v>0.0106</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7335</v>
+        <v>0.2811</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0443</v>
+        <v>-0.5756</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0015</v>
+        <v>-0.459</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0428</v>
+        <v>-0.1165</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4052</v>
+        <v>-1.1152</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0599</v>
+        <v>-0.2493</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3453</v>
+        <v>-0.8659</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.1587</v>
+        <v>-0.3373</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7458</v>
+        <v>0.8692</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4926</v>
+        <v>-1.2044</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7407</v>
+        <v>-0.5366</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7519</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3698</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7261</v>
+        <v>-0.4379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.352</v>
+        <v>-0.2678</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4312</v>
+        <v>-1.5147</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2392</v>
+        <v>-0.627</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1921</v>
+        <v>-0.8877</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5434</v>
@@ -2170,13 +2170,13 @@
         <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8716</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9352</v>
+        <v>-0.323</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9364</v>
+        <v>-0.6321</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7048</v>
+        <v>-2.5007</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6595</v>
+        <v>-0.4555</v>
       </c>
       <c r="F23" t="n">
         <v>-2.0452</v>
@@ -2248,10 +2248,10 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4737</v>
+        <v>-1.2697</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5611</v>
+        <v>-0.357</v>
       </c>
       <c r="U23" t="n">
         <v>-0.9126</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1389</v>
+        <v>-4.2426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0791</v>
+        <v>-0.3291</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2179</v>
+        <v>-3.9135</v>
       </c>
       <c r="G24" t="n">
         <v>0.0408</v>
@@ -2326,13 +2326,13 @@
         <v>2.579</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8343</v>
+        <v>-0.9381</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2382</v>
+        <v>-0.1699</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0725</v>
+        <v>-0.7681</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7502</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8496000000000006</v>
+        <v>1.529699999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>19.5056</v>
+        <v>19.5055</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.6561</v>
+        <v>-17.9758</v>
       </c>
       <c r="G25" t="n">
         <v>12.4577</v>
@@ -2404,13 +2404,13 @@
         <v>17.8546</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.6074</v>
+        <v>-8.9274</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6634</v>
+        <v>-2.6631</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.9441</v>
+        <v>-6.2639</v>
       </c>
       <c r="V25" t="n">
         <v>-8.9442</v>
